--- a/output/report.xlsx
+++ b/output/report.xlsx
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>441054.77</v>
+        <v>282120.59</v>
       </c>
     </row>
     <row r="33">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14992.78000000003</v>
+        <v>173926.96</v>
       </c>
     </row>
     <row r="34">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-103.7700000000186</v>
+        <v>158830.41</v>
       </c>
     </row>
     <row r="35">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9997647230977685</v>
+        <v>1.56298765715753</v>
       </c>
     </row>
     <row r="36">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.02352769022314816</v>
+        <v>56.29876571575295</v>
       </c>
     </row>
     <row r="37">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>9001.117755102041</v>
+        <v>5757.56306122449</v>
       </c>
     </row>
   </sheetData>
@@ -883,9 +883,9 @@
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
@@ -981,17 +981,17 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>webinar_type</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>registration_date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>registration_fee</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>webinar_type</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>registration_date</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -8084,7 +8084,7 @@
         <v/>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -8179,7 +8179,7 @@
         <v/>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -8274,7 +8274,7 @@
         <v/>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -8369,7 +8369,7 @@
         <v/>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -8464,7 +8464,7 @@
         <v/>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -8559,7 +8559,7 @@
         <v/>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -8654,7 +8654,7 @@
         <v/>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -8749,7 +8749,7 @@
         <v/>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -8844,7 +8844,7 @@
         <v/>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -8939,7 +8939,7 @@
         <v/>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -9034,7 +9034,7 @@
         <v/>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -9129,7 +9129,7 @@
         <v/>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -9224,7 +9224,7 @@
         <v/>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -9319,7 +9319,7 @@
         <v/>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -9414,7 +9414,7 @@
         <v/>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -9509,7 +9509,7 @@
         <v/>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -9604,7 +9604,7 @@
         <v/>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -9699,7 +9699,7 @@
         <v/>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -9794,7 +9794,7 @@
         <v/>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -9894,7 +9894,7 @@
         <v/>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -9989,7 +9989,7 @@
         <v/>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -10089,7 +10089,7 @@
         <v/>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -10184,7 +10184,7 @@
         <v/>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -10284,7 +10284,7 @@
         <v/>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -10384,7 +10384,7 @@
         <v/>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -10484,7 +10484,7 @@
         <v/>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -10579,7 +10579,7 @@
         <v/>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -10674,7 +10674,7 @@
         <v/>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -10769,7 +10769,7 @@
         <v/>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -10864,7 +10864,7 @@
         <v/>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -10959,7 +10959,7 @@
         <v/>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -11054,7 +11054,7 @@
         <v/>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -11149,7 +11149,7 @@
         <v/>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -11244,7 +11244,7 @@
         <v/>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -11339,7 +11339,7 @@
         <v/>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -11434,7 +11434,7 @@
         <v/>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -11529,7 +11529,7 @@
         <v/>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -11624,7 +11624,7 @@
         <v/>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -11719,7 +11719,7 @@
         <v/>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -11814,7 +11814,7 @@
         <v/>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -11909,7 +11909,7 @@
         <v/>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -12004,7 +12004,7 @@
         <v/>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -12099,7 +12099,7 @@
         <v/>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -12194,7 +12194,7 @@
         <v/>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -12289,7 +12289,7 @@
         <v/>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -12384,7 +12384,7 @@
         <v/>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -12479,7 +12479,7 @@
         <v/>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -12574,7 +12574,7 @@
         <v/>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -12669,7 +12669,7 @@
         <v/>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -12764,7 +12764,7 @@
         <v/>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -12859,7 +12859,7 @@
         <v/>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -12954,7 +12954,7 @@
         <v/>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -13049,7 +13049,7 @@
         <v/>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -13063,7 +13063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -13140,7 +13140,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -13148,11 +13148,13 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C:52.0, AS:52.0, AD:52.0</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
+          <t>C:49.0, AS:49.0, AD:49.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -13168,7 +13170,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -13176,11 +13178,13 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C:467948.0, AS:467948.0, AD:467948.0</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
+          <t>C:440951.0, AS:440951.0, AD:440951.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -13203,10 +13207,10 @@
         <v>456047.55</v>
       </c>
       <c r="D5" t="n">
-        <v>441054.77</v>
+        <v>282120.59</v>
       </c>
       <c r="E5" t="n">
-        <v>14992.78</v>
+        <v>173926.96</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -13453,6 +13457,422 @@
       <c r="F14" t="inlineStr">
         <is>
           <t>Count of sales that still lack a valid sale date</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>G. Total Sales</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>52</v>
+      </c>
+      <c r="D15" t="n">
+        <v>52</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Total Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>G. Attributed Sales</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>49</v>
+      </c>
+      <c r="D16" t="n">
+        <v>49</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Attributed Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>G. Unattributed Sales</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Unattributed Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>G. Total Revenue</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>467948</v>
+      </c>
+      <c r="D18" t="n">
+        <v>467948</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>G. Attributed Revenue</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>440951</v>
+      </c>
+      <c r="D19" t="n">
+        <v>440951</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Attributed Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>G. Unattributed Revenue</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>26997</v>
+      </c>
+      <c r="D20" t="n">
+        <v>26997</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Unattributed Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>G. Raw Meta Spend</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>456047.55</v>
+      </c>
+      <c r="D21" t="n">
+        <v>456047.55</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Raw Meta Spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>G. Attributed Spend</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>282120.59</v>
+      </c>
+      <c r="D22" t="n">
+        <v>282120.59</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Attributed Spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>G. Unallocated Spend</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>173926.96</v>
+      </c>
+      <c r="D23" t="n">
+        <v>173926.96</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Unallocated Spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>G. Profit</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>158830.41</v>
+      </c>
+      <c r="D24" t="n">
+        <v>158830.41</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>G. ROAS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Golden Report verification for ROAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>G. ROI %</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Golden Report verification for ROI %</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>G. CAC</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5757.56</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5757.56</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Golden Report verification for CAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>INV. Revenue Formula</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Attributed + Unattributed = Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>INV. Spend Formula</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Attributed + Unallocated = Raw Spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>INV. Profit Formula</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Attributed Revenue - Attributed Spend = Profit</t>
         </is>
       </c>
     </row>
@@ -13507,9 +13927,9 @@
     <col width="48" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
@@ -13605,17 +14025,17 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>webinar_type</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>registration_date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>registration_fee</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>webinar_type</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>registration_date</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -13722,18 +14142,18 @@
         </is>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>16700.66</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T2" s="3" t="n">
+      <c r="S2" s="3" t="n">
         <v>46248.79236111111</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -13837,16 +14257,16 @@
       <c r="Q3" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T3" s="3" t="n">
+      <c r="S3" s="3" t="n">
         <v>46243.98194444444</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -13950,16 +14370,16 @@
       <c r="Q4" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T4" s="3" t="n">
+      <c r="S4" s="3" t="n">
         <v>46245.31944444445</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -14036,10 +14456,10 @@
       <c r="Q5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="2" t="n">
-        <v/>
-      </c>
-      <c r="T5" s="3" t="n"/>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="2" t="n">
+        <v/>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>New</t>
@@ -14140,18 +14560,18 @@
         </is>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>8102.907000000001</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T6" s="3" t="n">
+      <c r="S6" s="3" t="n">
         <v>46243.91458333333</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -14253,18 +14673,18 @@
         </is>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>15081.1775</v>
-      </c>
-      <c r="R7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T7" s="3" t="n">
+      <c r="S7" s="3" t="n">
         <v>46247.64097222222</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -14368,16 +14788,16 @@
       <c r="Q8" s="2" t="n">
         <v>10080.81</v>
       </c>
-      <c r="R8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="S8" s="3" t="n">
         <v>46245.94930555556</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -14481,10 +14901,10 @@
       <c r="Q9" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R9" s="2" t="n">
-        <v/>
-      </c>
-      <c r="T9" s="3" t="n"/>
+      <c r="S9" s="3" t="n"/>
+      <c r="T9" s="2" t="n">
+        <v/>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>New</t>
@@ -14587,16 +15007,16 @@
       <c r="Q10" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T10" s="3" t="n">
+      <c r="S10" s="3" t="n">
         <v>46248.52986111111</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -14698,18 +15118,18 @@
         </is>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>879.74</v>
-      </c>
-      <c r="R11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T11" s="3" t="n">
+      <c r="S11" s="3" t="n">
         <v>46249.45555555556</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -14813,10 +15233,10 @@
       <c r="Q12" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R12" s="2" t="n">
-        <v/>
-      </c>
-      <c r="T12" s="3" t="n"/>
+      <c r="S12" s="3" t="n"/>
+      <c r="T12" s="2" t="n">
+        <v/>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>New</t>
@@ -14919,16 +15339,16 @@
       <c r="Q13" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T13" s="3" t="n">
+      <c r="S13" s="3" t="n">
         <v>46244.9875</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -15032,16 +15452,16 @@
       <c r="Q14" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T14" s="3" t="n">
+      <c r="S14" s="3" t="n">
         <v>46248.38263888889</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -15143,18 +15563,18 @@
         </is>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>8102.907000000001</v>
-      </c>
-      <c r="R15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T15" s="3" t="n">
+      <c r="S15" s="3" t="n">
         <v>46247.81805555556</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -15258,16 +15678,16 @@
       <c r="Q16" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T16" s="3" t="n">
+      <c r="S16" s="3" t="n">
         <v>46247.56875</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -15369,12 +15789,12 @@
         </is>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>8102.907000000001</v>
-      </c>
-      <c r="R17" s="2" t="n">
-        <v/>
-      </c>
-      <c r="T17" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="3" t="n"/>
+      <c r="T17" s="2" t="n">
+        <v/>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>New</t>
@@ -15477,16 +15897,16 @@
       <c r="Q18" s="2" t="n">
         <v>10080.81</v>
       </c>
-      <c r="R18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T18" s="3" t="n">
+      <c r="S18" s="3" t="n">
         <v>46248.38333333333</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -15563,10 +15983,10 @@
       <c r="Q19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R19" s="2" t="n">
-        <v/>
-      </c>
-      <c r="T19" s="3" t="n"/>
+      <c r="S19" s="3" t="n"/>
+      <c r="T19" s="2" t="n">
+        <v/>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>New</t>
@@ -15669,16 +16089,16 @@
       <c r="Q20" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T20" s="3" t="n">
+      <c r="S20" s="3" t="n">
         <v>46244.35347222222</v>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -15782,16 +16202,16 @@
       <c r="Q21" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T21" s="3" t="n">
+      <c r="S21" s="3" t="n">
         <v>46243.49444444444</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -15893,18 +16313,18 @@
         </is>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>8102.907000000001</v>
-      </c>
-      <c r="R22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T22" s="3" t="n">
+      <c r="S22" s="3" t="n">
         <v>46245.81666666667</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -16008,10 +16428,10 @@
       <c r="Q23" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R23" s="2" t="n">
-        <v/>
-      </c>
-      <c r="T23" s="3" t="n"/>
+      <c r="S23" s="3" t="n"/>
+      <c r="T23" s="2" t="n">
+        <v/>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>New</t>
@@ -16114,16 +16534,16 @@
       <c r="Q24" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T24" s="3" t="n">
+      <c r="S24" s="3" t="n">
         <v>46247.375</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -16227,16 +16647,16 @@
       <c r="Q25" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T25" s="3" t="n">
+      <c r="S25" s="3" t="n">
         <v>46245.99861111111</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -16338,18 +16758,18 @@
         </is>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>15081.1775</v>
-      </c>
-      <c r="R26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T26" s="3" t="n">
+      <c r="S26" s="3" t="n">
         <v>46247.32152777778</v>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -16451,12 +16871,12 @@
         </is>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>8102.907000000001</v>
-      </c>
-      <c r="R27" s="2" t="n">
-        <v/>
-      </c>
-      <c r="T27" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="3" t="n"/>
+      <c r="T27" s="2" t="n">
+        <v/>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>New</t>
@@ -16532,16 +16952,16 @@
       <c r="Q28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T28" s="3" t="n">
+      <c r="S28" s="3" t="n">
         <v>46245.96875</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -16645,16 +17065,16 @@
       <c r="Q29" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T29" s="3" t="n">
+      <c r="S29" s="3" t="n">
         <v>46244.92986111111</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -16756,18 +17176,18 @@
         </is>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>8102.907000000001</v>
-      </c>
-      <c r="R30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T30" s="3" t="n">
+      <c r="S30" s="3" t="n">
         <v>46247.72847222222</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -16869,12 +17289,12 @@
         </is>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>8102.907000000001</v>
-      </c>
-      <c r="R31" s="2" t="n">
-        <v/>
-      </c>
-      <c r="T31" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="3" t="n"/>
+      <c r="T31" s="2" t="n">
+        <v/>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>New</t>
@@ -16977,16 +17397,16 @@
       <c r="Q32" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T32" s="3" t="n">
+      <c r="S32" s="3" t="n">
         <v>46243.63055555556</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -17090,16 +17510,16 @@
       <c r="Q33" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T33" s="3" t="n">
+      <c r="S33" s="3" t="n">
         <v>46246.63958333333</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -17203,10 +17623,10 @@
       <c r="Q34" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R34" s="2" t="n">
-        <v/>
-      </c>
-      <c r="T34" s="3" t="n"/>
+      <c r="S34" s="3" t="n"/>
+      <c r="T34" s="2" t="n">
+        <v/>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>New</t>
@@ -17309,16 +17729,16 @@
       <c r="Q35" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T35" s="3" t="n">
+      <c r="S35" s="3" t="n">
         <v>46248.97569444445</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -17420,18 +17840,18 @@
         </is>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>8102.907000000001</v>
-      </c>
-      <c r="R36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T36" s="3" t="n">
+      <c r="S36" s="3" t="n">
         <v>46247.53958333333</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -17533,18 +17953,18 @@
         </is>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>8102.907000000001</v>
-      </c>
-      <c r="R37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T37" s="3" t="n">
+      <c r="S37" s="3" t="n">
         <v>46245.68472222222</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -17648,16 +18068,16 @@
       <c r="Q38" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T38" s="3" t="n">
+      <c r="S38" s="3" t="n">
         <v>46247.77708333333</v>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -17761,10 +18181,10 @@
       <c r="Q39" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R39" s="2" t="n">
-        <v/>
-      </c>
-      <c r="T39" s="3" t="n"/>
+      <c r="S39" s="3" t="n"/>
+      <c r="T39" s="2" t="n">
+        <v/>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>New</t>
@@ -17867,16 +18287,16 @@
       <c r="Q40" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T40" s="3" t="n">
+      <c r="S40" s="3" t="n">
         <v>46245.82361111111</v>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -17980,16 +18400,16 @@
       <c r="Q41" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T41" s="3" t="n">
+      <c r="S41" s="3" t="n">
         <v>46245.41875</v>
+      </c>
+      <c r="T41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -18093,10 +18513,10 @@
       <c r="Q42" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R42" s="2" t="n">
-        <v/>
-      </c>
-      <c r="T42" s="3" t="n"/>
+      <c r="S42" s="3" t="n"/>
+      <c r="T42" s="2" t="n">
+        <v/>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
           <t>New</t>
@@ -18197,12 +18617,12 @@
         </is>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>15081.1775</v>
-      </c>
-      <c r="R43" s="2" t="n">
-        <v/>
-      </c>
-      <c r="T43" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="3" t="n"/>
+      <c r="T43" s="2" t="n">
+        <v/>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>New</t>
@@ -18305,16 +18725,16 @@
       <c r="Q44" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T44" s="3" t="n">
+      <c r="S44" s="3" t="n">
         <v>46244.30694444444</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -18418,16 +18838,16 @@
       <c r="Q45" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T45" s="3" t="n">
+      <c r="S45" s="3" t="n">
         <v>46248.91944444444</v>
+      </c>
+      <c r="T45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -18531,16 +18951,16 @@
       <c r="Q46" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T46" s="3" t="n">
+      <c r="S46" s="3" t="n">
         <v>46243.27708333333</v>
+      </c>
+      <c r="T46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -18644,10 +19064,10 @@
       <c r="Q47" s="2" t="n">
         <v>10080.81</v>
       </c>
-      <c r="R47" s="2" t="n">
-        <v/>
-      </c>
-      <c r="T47" s="3" t="n"/>
+      <c r="S47" s="3" t="n"/>
+      <c r="T47" s="2" t="n">
+        <v/>
+      </c>
       <c r="U47" t="inlineStr">
         <is>
           <t>New</t>
@@ -18750,16 +19170,16 @@
       <c r="Q48" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T48" s="3" t="n">
+      <c r="S48" s="3" t="n">
         <v>46246.52708333333</v>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -18861,18 +19281,18 @@
         </is>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>15081.1775</v>
-      </c>
-      <c r="R49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R49" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T49" s="3" t="n">
+      <c r="S49" s="3" t="n">
         <v>46243.63333333333</v>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -18976,16 +19396,16 @@
       <c r="Q50" s="2" t="n">
         <v>10080.81</v>
       </c>
-      <c r="R50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T50" s="3" t="n">
+      <c r="S50" s="3" t="n">
         <v>46249.40625</v>
+      </c>
+      <c r="T50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -19087,18 +19507,18 @@
         </is>
       </c>
       <c r="Q51" s="2" t="n">
-        <v>8102.907000000001</v>
-      </c>
-      <c r="R51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R51" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T51" s="3" t="n">
+      <c r="S51" s="3" t="n">
         <v>46248.67083333333</v>
+      </c>
+      <c r="T51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -19203,10 +19623,10 @@
       <c r="Q52" s="2" t="n">
         <v>10080.81</v>
       </c>
-      <c r="R52" s="2" t="n">
-        <v/>
-      </c>
-      <c r="T52" s="3" t="n"/>
+      <c r="S52" s="3" t="n"/>
+      <c r="T52" s="2" t="n">
+        <v/>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>New</t>
@@ -19309,10 +19729,10 @@
       <c r="Q53" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="R53" s="2" t="n">
-        <v/>
-      </c>
-      <c r="T53" s="3" t="n"/>
+      <c r="S53" s="3" t="n"/>
+      <c r="T53" s="2" t="n">
+        <v/>
+      </c>
       <c r="U53" t="inlineStr">
         <is>
           <t>New</t>
@@ -19346,7 +19766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M119"/>
+  <dimension ref="A1:M118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -19508,16 +19928,22 @@
         <v>89990</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>8960.929999999993</v>
-      </c>
-      <c r="J3" s="6" t="n">
-        <v>1.110589076241403</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>11.05890762414031</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>8102.907000000001</v>
+        <v>89990</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -19601,55 +20027,61 @@
       <c r="H5" s="2" t="n">
         <v>35996</v>
       </c>
-      <c r="I5" s="7" t="n">
-        <v>-24328.71</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>0.5967040703552491</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>-40.32959296447508</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>15081.1775</v>
+      <c r="I5" s="5" t="n">
+        <v>35996</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>foremost leads | cbo | 11th august 2026</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>16700.66</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>54</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>309.2714814814815</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1.851851851851852</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>26997</v>
+        <v>8999</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>26997</v>
+        <v>8999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -19675,7 +20107,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026</t>
+          <t>foremost leads | cbo | 14th august</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -19684,45 +20116,51 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>16700.66</v>
+        <v>879.74</v>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>309.2714814814815</v>
+        <v>79.97636363636364</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.851851851851852</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>8999</v>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>-7701.66</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>0.5388409799373198</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>-46.11590200626802</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>16700.66</v>
+      <c r="I7" s="5" t="n">
+        <v>8999</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august</t>
+          <t>fml-test-002</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -19731,45 +20169,55 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>879.74</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>79.97636363636364</v>
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>9.090909090909092</v>
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>8119.26</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>10.22915861504536</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>922.9158615045355</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>879.74</v>
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fml-test-002</t>
+          <t>foremost leads &lt;&gt; 2103</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -19826,7 +20274,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 2103</t>
+          <t>foremost</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -19838,20 +20286,16 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G10" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>0</v>
@@ -19883,7 +20327,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>foremost</t>
+          <t>fml-x1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -19895,16 +20339,20 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="4" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H11" s="2" t="n">
         <v>0</v>
@@ -19936,7 +20384,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fml-x1</t>
+          <t>fml-test-open</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -19993,7 +20441,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fml-test-open</t>
+          <t>fml-test-instant-form</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -20050,7 +20498,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fml-test-instant-form</t>
+          <t>fml-test-campaign-all</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -20107,7 +20555,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fml-test-campaign-all</t>
+          <t>fml-test-campaign</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -20164,7 +20612,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fml-test-campaign</t>
+          <t>fml-test-1nov</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -20221,7 +20669,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fml-test-1nov</t>
+          <t>--</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -20233,20 +20681,16 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>0</v>
@@ -20278,7 +20722,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fml-test campaign</t>
+          <t>foremost leads &lt;&gt; 2103 cbo lla &lt;&gt; s2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -20335,7 +20779,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 2103 cbo lla &lt;&gt; s2</t>
+          <t>fml-test campaign</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -21072,7 +21516,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fml-cbo-travel-001</t>
+          <t>foremost leads &lt;&gt; 2103 cbo [22-4-26]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -21129,7 +21573,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 2103 cbo [22-4-26]</t>
+          <t>foremost leads &lt;&gt; 2103 cbo1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -21186,7 +21630,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 2103 cbo1</t>
+          <t>foremost leads &lt;&gt; 2103 cbo lla &lt;&gt; s3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -21243,7 +21687,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 2103 cbo lla &lt;&gt; s3</t>
+          <t>foremost leads &lt;&gt; 2103 cbo s2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -21300,7 +21744,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 2103 cbo s2</t>
+          <t>retargeting-campaign [22-12-25]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -21357,7 +21801,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>retargeting-campaign [22-12-25]</t>
+          <t>p1-abo xx [22-12-25] xx [24-12-25]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -21414,7 +21858,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>p1-abo xx [22-12-25] xx [24-12-25]</t>
+          <t>p1 - abo 2 xx [22-12-25] xx [24-12-25]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -21471,7 +21915,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>p1 - abo 2 xx [22-12-25] xx [24-12-25]</t>
+          <t>new sales campaign</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -21528,7 +21972,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>new sales campaign</t>
+          <t>new leads campaign</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -21585,7 +22029,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>new leads campaign</t>
+          <t>formost leads &lt;&gt; video &lt;&gt; talking head &lt;&gt; cbo | 74852</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -21642,7 +22086,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>formost leads &lt;&gt; video &lt;&gt; talking head &lt;&gt; cbo | 74852</t>
+          <t>foremostleads-gs-13-095</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -21699,7 +22143,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-095</t>
+          <t>foremostleads-gs-13-09-10-video ads</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -21756,7 +22200,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09-10-video ads</t>
+          <t>foremostleads-gs-13-09- simple image ads</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -21813,7 +22257,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09- simple image ads</t>
+          <t>foremostleads-gs-13-09- 10 video</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -21870,7 +22314,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09- 10 video</t>
+          <t>foremostleads-gs-13-09 7 video ads</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -21927,7 +22371,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 7 video ads</t>
+          <t>foremostleads-gs-13-09 4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -21984,7 +22428,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 4</t>
+          <t>foremostleads-gs-13-09 3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -22041,7 +22485,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 3</t>
+          <t>foremostleads + rky+ 23/04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -22098,7 +22542,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>foremostleads + rky+ 23/04</t>
+          <t>foremostleads + rky+ 22/04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -22155,7 +22599,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>foremostleads + rky+ 22/04</t>
+          <t>foremostleads + rky+ 19/04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22212,7 +22656,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>foremostleads + rky+ 19/04</t>
+          <t>foremostleads + rky+ 09/04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22269,7 +22713,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>foremostleads + rky+ 09/04</t>
+          <t>foremost leads | cbo | 5th aug 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -22278,23 +22722,19 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>0</v>
+        <v>14992.78</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>68</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>220.4820588235294</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G53" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
@@ -22326,7 +22766,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026</t>
+          <t>foremost leads &lt;&gt; test &lt;&gt; 18/07/26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -22335,19 +22775,23 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>14992.78</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>68</v>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>220.4820588235294</v>
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
-      <c r="G54" s="4" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H54" s="2" t="n">
         <v>0</v>
@@ -22379,7 +22823,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; test &lt;&gt; 18/07/26</t>
+          <t>foremost leads &lt;&gt; ry &lt;&gt; 11/06 &lt;&gt; abo</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -22436,7 +22880,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; ry &lt;&gt; 11/06 &lt;&gt; abo</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; cc297623 | images</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -22493,7 +22937,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; cc297623 | images</t>
+          <t>foremost leads &lt;&gt; 2103 open</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -22550,7 +22994,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 2103 open</t>
+          <t>fml-cbo-test – copy</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -22607,7 +23051,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>fml-cbo-travel-001</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -22619,16 +23063,20 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>21</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
-      <c r="G59" s="4" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H59" s="2" t="n">
         <v>0</v>
@@ -22660,7 +23108,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>fml-cbo-test – copy</t>
+          <t>fml-cbo-test</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -22717,7 +23165,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>fml-cbo-test</t>
+          <t>cbo_all videos_28/03</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -22774,7 +23222,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>fml-cbo-p2</t>
+          <t>fml-abo-c2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -22831,7 +23279,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>fml-abo-c1</t>
+          <t>fml-c1-broad - travel interests</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -23515,7 +23963,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>fml-abo-c2</t>
+          <t>fml-abo-c1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -23572,7 +24020,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>fml-abo [22-12-25]</t>
+          <t>fml-cbo-p2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -23629,7 +24077,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>fml-cbo-og</t>
+          <t>fml-abo [22-12-25]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -24309,7 +24757,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>cbo_all videos_28/03</t>
+          <t>fml-c1-broad - travel interests – copy</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -24366,7 +24814,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>fml-c1-broad - travel interests</t>
+          <t>fml-c1-travel</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -24423,7 +24871,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>fml-c1-broad - travel interests – copy</t>
+          <t>fml-c1-wn</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -24480,7 +24928,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>fml-c1-travel</t>
+          <t>fml-c1-wn [03-01-26]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -24537,7 +24985,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>fml-c1-wn</t>
+          <t>fml-cbo-og</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -25962,7 +26410,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>fml-c1-wn [03-01-26]</t>
+          <t>{{campaign.name}}</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -25974,20 +26422,16 @@
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>45</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G118" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
         <v>0</v>
@@ -26011,59 +26455,6 @@
         </is>
       </c>
       <c r="M118" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>{{campaign.name}}</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" t="n">
-        <v>45</v>
-      </c>
-      <c r="E119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -26080,7 +26471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -26168,7 +26559,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &gt; </t>
+          <t>-- &gt; --</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -26180,26 +26571,22 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>26997</v>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -26218,14 +26605,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-- &gt; --</t>
+          <t>chatgpt.com &gt; --</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -26237,7 +26624,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
@@ -26278,7 +26665,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>chatgpt.com &gt; --</t>
+          <t>fml-p1-002 &gt; coding languages – copy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -26331,7 +26718,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fml-p1-002 &gt; coding languages – copy</t>
+          <t>foremost &gt; --</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -26384,7 +26771,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>foremost &gt; --</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -26393,51 +26780,45 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>118171.8760061444</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>951</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>124.2606477456828</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>1.366982124079916</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>116987</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>9404.320714285714</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.08741482157467</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>8.741482157467049</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -26446,31 +26827,31 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>118171.8760061444</v>
+        <v>22068.2419047619</v>
       </c>
       <c r="D7" t="n">
-        <v>951</v>
+        <v>171</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>124.2606477456828</v>
+        <v>129.0540462266778</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.366982124079916</v>
+        <v>2.923976608187134</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>116987</v>
+        <v>44995</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>9404.320714285714</v>
+        <v>3617.046428571426</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>1.08741482157467</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.741482157467049</v>
+        <v>8.741482157467043</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>8275.590714285714</v>
@@ -26484,7 +26865,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -26493,31 +26874,31 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>22068.2419047619</v>
+        <v>56950.30168970814</v>
       </c>
       <c r="D8" t="n">
-        <v>171</v>
+        <v>457</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>129.0540462266778</v>
+        <v>124.6177279862323</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.923976608187134</v>
+        <v>1.75054704595186</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>44995</v>
+        <v>71992</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>3617.046428571426</v>
+        <v>5787.274285714288</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>1.08741482157467</v>
+        <v>1.087414821574671</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.741482157467043</v>
+        <v>8.741482157467054</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>8275.590714285714</v>
@@ -26531,7 +26912,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -26540,25 +26921,25 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>56950.30168970814</v>
+        <v>34526.12039938556</v>
       </c>
       <c r="D9" t="n">
-        <v>457</v>
+        <v>273</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>124.6177279862323</v>
+        <v>126.4693054922548</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.75054704595186</v>
+        <v>0.7326007326007326</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>71992</v>
+        <v>17998</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>5787.274285714288</v>
+        <v>1446.818571428572</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>1.087414821574671</v>
@@ -26578,7 +26959,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -26587,45 +26968,51 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>34526.12039938556</v>
+        <v>851.4197635135137</v>
       </c>
       <c r="D10" t="n">
-        <v>273</v>
+        <v>10</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>126.4693054922548</v>
+        <v>85.14197635135136</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.7326007326007326</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>17998</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>1446.818571428572</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>1.087414821574671</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>8.741482157467054</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>8275.590714285714</v>
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -26634,40 +27021,34 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>851.4197635135137</v>
+        <v>49552.63023648649</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>548</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>85.14197635135136</v>
+        <v>90.42450773081477</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0</v>
+        <v>0.9124087591240875</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>44995</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>-5409.050000000003</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>0.8926862027952118</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>-10.73137972047882</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>10080.81</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -26678,7 +27059,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -26687,45 +27068,51 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>49552.63023648649</v>
+        <v>31841.00074647887</v>
       </c>
       <c r="D12" t="n">
-        <v>548</v>
+        <v>269</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>90.42450773081477</v>
+        <v>118.3680325147914</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.9124087591240875</v>
+        <v>1.115241635687732</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>-5409.050000000003</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>0.8926862027952118</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>-10.73137972047882</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>10080.81</v>
+        <v>26997</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>26997</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -26734,34 +27121,40 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>31841.00074647887</v>
+        <v>49188.06925352113</v>
       </c>
       <c r="D13" t="n">
-        <v>269</v>
+        <v>416</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>118.3680325147914</v>
+        <v>118.240551090195</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.115241635687732</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>26997</v>
+        <v>62993</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>2688.278999999995</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>1.110589076241403</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>11.0589076241403</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>8102.907000000002</v>
+        <v>62993</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -26772,7 +27165,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -26781,45 +27174,51 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>49188.06925352113</v>
+        <v>1415.310169491525</v>
       </c>
       <c r="D14" t="n">
-        <v>416</v>
+        <v>5</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>118.240551090195</v>
+        <v>283.0620338983051</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.682692307692308</v>
+        <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>62993</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>6272.650999999991</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>1.110589076241403</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>11.05890762414031</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>8102.907000000001</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -26828,13 +27227,13 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1415.310169491525</v>
+        <v>8208.798983050849</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>283.0620338983051</v>
+        <v>342.033290960452</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -26872,7 +27271,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -26881,25 +27280,25 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>8208.798983050849</v>
+        <v>7076.550847457626</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>342.033290960452</v>
+        <v>283.0620338983051</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -26918,14 +27317,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55</t>
+          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -26934,45 +27333,51 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>7076.550847457626</v>
+        <v>537.6188888888889</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>283.0620338983051</v>
+        <v>134.4047222222222</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>8999</v>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>-7701.66</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>0.5388409799373198</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>-46.11590200626802</v>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>16700.66</v>
+      <c r="I17" s="5" t="n">
+        <v>8999</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55</t>
+          <t>foremost leads | cbo | 14th august &gt; core it professionals | 25 - 55</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -26981,45 +27386,51 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>537.6188888888889</v>
+        <v>342.1211111111111</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>134.4047222222222</v>
+        <v>48.87444444444445</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>8119.26</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>10.22915861504536</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>922.9158615045355</v>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>879.74</v>
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; core it professionals | 25 - 55</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 |</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -27028,13 +27439,13 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>342.1211111111111</v>
+        <v>1102.410294117647</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>48.87444444444445</v>
+        <v>220.4820588235295</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -27072,7 +27483,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 |</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 |</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -27081,13 +27492,13 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1102.410294117647</v>
+        <v>6173.497647058824</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>220.4820588235295</v>
+        <v>220.4820588235294</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -27125,7 +27536,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 |</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 |</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -27134,10 +27545,10 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>6173.497647058824</v>
+        <v>1763.856470588235</v>
       </c>
       <c r="D21" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>220.4820588235294</v>
@@ -27178,7 +27589,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 |</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 |</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -27187,10 +27598,10 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>1763.856470588235</v>
+        <v>5953.015588235294</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>220.4820588235294</v>
@@ -27231,7 +27642,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 |</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -27240,25 +27651,25 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5953.015588235294</v>
+        <v>60324.71</v>
       </c>
       <c r="D23" t="n">
-        <v>27</v>
+        <v>237</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>220.4820588235294</v>
+        <v>254.534641350211</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0</v>
+        <v>1.687763713080169</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>35996</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>35996</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -27277,14 +27688,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open</t>
+          <t>{{campaign.name}} &gt; {{adset.name}}</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -27293,89 +27704,42 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>60324.71</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>237</v>
+        <v>45</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>254.534641350211</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.687763713080169</v>
+        <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>35996</v>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>-24328.71</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>0.5967040703552491</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>-40.32959296447508</v>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>15081.1775</v>
+        <v>0</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M24" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>{{campaign.name}} &gt; {{adset.name}}</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>45</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -27392,7 +27756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -27480,7 +27844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &gt;  &gt; </t>
+          <t>-- &gt; -- &gt; --</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -27492,26 +27856,22 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>26997</v>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -27530,14 +27890,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-- &gt; -- &gt; --</t>
+          <t>chatgpt.com &gt; -- &gt; --</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -27549,7 +27909,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
@@ -27590,7 +27950,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>chatgpt.com &gt; -- &gt; --</t>
+          <t>fml-p1-002 &gt; coding languages – copy &gt; abhishekpal-ad 2 hook 6-1;1 ratio-311025-006</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -27643,7 +28003,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fml-p1-002 &gt; coding languages – copy &gt; abhishekpal-ad 2 hook 6-1;1 ratio-311025-006</t>
+          <t>foremost &gt; -- &gt; --</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -27696,7 +28056,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>foremost &gt; -- &gt; --</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience &gt; split screen &lt;&gt; germany is actively hiring international talent right now &gt;</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -27705,51 +28065,45 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>118171.8760061444</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>951</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>124.2606477456828</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>1.366982124079916</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>116987</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>9404.320714285714</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.08741482157467</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>8.741482157467049</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience &gt; split screen &lt;&gt; germany is actively hiring international talent right now &gt;</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy &gt; image ad &lt;&gt; sticky note &lt;&gt; join this masterclass, dubai's tech sector is growing fast and sponsoring visas now</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -27758,31 +28112,31 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>118171.8760061444</v>
+        <v>22068.2419047619</v>
       </c>
       <c r="D7" t="n">
-        <v>951</v>
+        <v>171</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>124.2606477456828</v>
+        <v>129.0540462266778</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.366982124079916</v>
+        <v>2.923976608187134</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>116987</v>
+        <v>44995</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>9404.320714285714</v>
+        <v>3617.046428571426</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>1.08741482157467</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.741482157467049</v>
+        <v>8.741482157467043</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>8275.590714285714</v>
@@ -27796,7 +28150,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy &gt; image ad &lt;&gt; sticky note &lt;&gt; join this masterclass, dubai's tech sector is growing fast and sponsoring visas now</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -27805,19 +28159,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>22068.2419047619</v>
+        <v>28593.79730670763</v>
       </c>
       <c r="D8" t="n">
-        <v>171</v>
+        <v>230</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>129.0540462266778</v>
+        <v>124.3208578552506</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.923976608187134</v>
+        <v>2.173913043478261</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>44995</v>
@@ -27843,7 +28197,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; if you want a it job abroad in 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -27852,45 +28206,51 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>28593.79730670763</v>
+        <v>949.1716948284691</v>
       </c>
       <c r="D9" t="n">
-        <v>230</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>124.3208578552506</v>
+        <v>118.6464618535586</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.173913043478261</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>3617.046428571426</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>1.08741482157467</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>8.741482157467043</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>8275.590714285714</v>
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; if you want a it job abroad in 2026</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; what if i get rejected my english not that good &lt;&gt; navy blue blazer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -27899,51 +28259,45 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>949.1716948284691</v>
+        <v>27407.33268817205</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>219</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>118.6464618535586</v>
+        <v>125.1476378455345</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>1.36986301369863</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>26997</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>2170.227857142858</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>1.087414821574671</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>8.741482157467054</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; what if i get rejected my english not that good &lt;&gt; navy blue blazer</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; laptop screen | if you're an it professional in india &amp; looking to get</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -27952,45 +28306,51 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>27407.33268817205</v>
+        <v>118.6464618535586</v>
       </c>
       <c r="D11" t="n">
-        <v>219</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>125.1476378455345</v>
+        <v>118.6464618535586</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.36986301369863</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>2170.227857142858</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>1.087414821574671</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>8.741482157467054</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>8275.590714285714</v>
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; laptop screen | if you're an it professional in india &amp; looking to get</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -27999,51 +28359,45 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>118.6464618535586</v>
+        <v>34407.47393753201</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>272</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>118.6464618535586</v>
+        <v>126.4980659468089</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0</v>
+        <v>0.7352941176470588</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>17998</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1446.818571428572</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.087414821574671</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>8.741482157467054</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -28052,45 +28406,51 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>34407.47393753201</v>
+        <v>851.4197635135137</v>
       </c>
       <c r="D13" t="n">
-        <v>272</v>
+        <v>10</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>126.4980659468089</v>
+        <v>85.14197635135136</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.7352941176470588</v>
+        <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>17998</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>1446.818571428572</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>1.087414821574671</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>8.741482157467054</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>8275.590714285714</v>
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -28099,40 +28459,34 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>851.4197635135137</v>
+        <v>49552.63023648649</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>548</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>85.14197635135136</v>
+        <v>90.42450773081477</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0</v>
+        <v>0.9124087591240875</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>44995</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>-5409.050000000003</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>0.8926862027952118</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>-10.73137972047882</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>10080.81</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -28143,7 +28497,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; --</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -28152,34 +28506,40 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>49552.63023648649</v>
+        <v>114.1254507042254</v>
       </c>
       <c r="D15" t="n">
-        <v>548</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>90.42450773081477</v>
+        <v>114.1254507042254</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.9124087591240875</v>
+        <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>-5409.050000000003</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>0.8926862027952118</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>-10.73137972047882</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>10080.81</v>
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -28190,7 +28550,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; --</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt; – copy 2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -28243,7 +28603,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt; – copy 2</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09&lt;attention it professionals if you are an it engineer&gt; – copy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -28252,25 +28612,25 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>114.1254507042254</v>
+        <v>31612.74984507042</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>267</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>114.1254507042254</v>
+        <v>118.3998121538218</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0</v>
+        <v>1.123595505617978</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>26997</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>26997</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -28289,14 +28649,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09&lt;attention it professionals if you are an it engineer&gt; – copy</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremost leads-13-09&lt;do you know which countries are hiring&gt; – copy 2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -28305,45 +28665,51 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>31612.74984507042</v>
+        <v>114.1254507042254</v>
       </c>
       <c r="D18" t="n">
-        <v>267</v>
+        <v>1</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>118.3998121538218</v>
+        <v>114.1254507042254</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.123595505617978</v>
+        <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>2688.278999999995</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>1.110589076241403</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>11.0589076241403</v>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>8102.907000000002</v>
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremost leads-13-09&lt;do you know which countries are hiring&gt; – copy 2</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremostleads-gs-13-09&lt;do you know which countries are actively sponsoring visas&gt; – copy 2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -28352,25 +28718,25 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>114.1254507042254</v>
+        <v>49073.9438028169</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>415</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>114.1254507042254</v>
+        <v>118.2504669947395</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0</v>
+        <v>1.686746987951807</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>62993</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>62993</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -28389,14 +28755,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremostleads-gs-13-09&lt;do you know which countries are actively sponsoring visas&gt; – copy 2</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55 &gt; split ad 10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -28405,45 +28771,51 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>49073.9438028169</v>
+        <v>849.1861016949154</v>
       </c>
       <c r="D20" t="n">
-        <v>415</v>
+        <v>3</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>118.2504669947395</v>
+        <v>283.0620338983051</v>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.686746987951807</v>
+        <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>62993</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>6272.650999999991</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>1.110589076241403</v>
-      </c>
-      <c r="K20" s="4" t="n">
-        <v>11.05890762414031</v>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>8102.907000000001</v>
+        <v>0</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55 &gt; split ad 10</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55 &gt; split ad 4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -28452,10 +28824,10 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>849.1861016949154</v>
+        <v>566.1240677966101</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>283.0620338983051</v>
@@ -28496,7 +28868,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55 &gt; split ad 4</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55 &gt; split ad 1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -28505,13 +28877,13 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>566.1240677966101</v>
+        <v>1981.434237288136</v>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>283.0620338983051</v>
+        <v>990.7171186440678</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -28549,7 +28921,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55 &gt; split ad 1</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55 &gt; split ad 2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -28558,13 +28930,13 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1981.434237288136</v>
+        <v>6227.364745762712</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>990.7171186440678</v>
+        <v>283.0620338983051</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -28602,7 +28974,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55 &gt; split ad 2</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -28611,10 +28983,10 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>6227.364745762712</v>
+        <v>4245.930508474576</v>
       </c>
       <c r="D24" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>283.0620338983051</v>
@@ -28655,7 +29027,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 5</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -28664,10 +29036,10 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>4245.930508474576</v>
+        <v>1981.434237288136</v>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>283.0620338983051</v>
@@ -28708,7 +29080,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 6</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -28717,25 +29089,25 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>1981.434237288136</v>
+        <v>849.1861016949154</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>283.0620338983051</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -28754,14 +29126,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 7</t>
+          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -28770,34 +29142,40 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>849.1861016949154</v>
+        <v>48.87444444444444</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>283.0620338983051</v>
+        <v>48.87444444444444</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I27" s="7" t="n">
-        <v>-7701.66</v>
-      </c>
-      <c r="J27" s="6" t="n">
-        <v>0.5388409799373198</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>-46.11590200626802</v>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>16700.66</v>
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -28808,7 +29186,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 1</t>
+          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -28817,25 +29195,25 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>48.87444444444444</v>
+        <v>488.7444444444445</v>
       </c>
       <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>162.9148148148148</v>
+      </c>
+      <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>48.87444444444444</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" s="4" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -28854,14 +29232,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 2</t>
+          <t>foremost leads | cbo | 14th august &gt; core it professionals | 25 - 55 &gt; abhishek pal 5</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -28870,45 +29248,51 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>488.7444444444445</v>
+        <v>342.1211111111111</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>162.9148148148148</v>
+        <v>48.87444444444445</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>8119.26</v>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>10.22915861504536</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>922.9158615045355</v>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>879.74</v>
+        <v>0</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; core it professionals | 25 - 55 &gt; abhishek pal 5</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | dubai's tech sector is growing fast and sponsoring visas now</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -28917,13 +29301,13 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>342.1211111111111</v>
+        <v>220.4820588235294</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>48.87444444444445</v>
+        <v>220.4820588235294</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -28961,7 +29345,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | dubai's tech sector is growing fast and sponsoring visas now</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | stop applying to places that were never going to sponsor you. find out who actually does</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -28970,10 +29354,10 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>220.4820588235294</v>
+        <v>881.9282352941177</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>220.4820588235294</v>
@@ -29014,7 +29398,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | stop applying to places that were never going to sponsor you. find out who actually does</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 | &gt; image ads | whiteboard | pick the right country for your experience. not just what's trending</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -29023,10 +29407,10 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>881.9282352941177</v>
+        <v>6173.497647058824</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>220.4820588235294</v>
@@ -29067,7 +29451,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 | &gt; image ads | whiteboard | pick the right country for your experience. not just what's trending</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | sticky notes | germany is short on tech workers and hiring from india right now</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -29076,10 +29460,10 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>6173.497647058824</v>
+        <v>1543.374411764706</v>
       </c>
       <c r="D33" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>220.4820588235294</v>
@@ -29120,7 +29504,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | sticky notes | germany is short on tech workers and hiring from india right now</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | whiteboard | know what dutch companies look for before you apply</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -29129,10 +29513,10 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>1543.374411764706</v>
+        <v>220.4820588235294</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>220.4820588235294</v>
@@ -29173,7 +29557,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | whiteboard | know what dutch companies look for before you apply</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 | &gt; image ads | ignored vs shortlisted</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -29182,10 +29566,10 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>220.4820588235294</v>
+        <v>5953.015588235294</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>220.4820588235294</v>
@@ -29226,7 +29610,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 | &gt; image ads | ignored vs shortlisted</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504(1).mp4&gt;</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -29235,25 +29619,25 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>5953.015588235294</v>
+        <v>17817.42489451477</v>
       </c>
       <c r="D36" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>220.4820588235294</v>
+        <v>254.534641350211</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
+        <v>26997</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>26997</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -29272,14 +29656,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504(1).mp4&gt;</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt;</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -29288,45 +29672,51 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>17817.42489451477</v>
+        <v>42507.28510548524</v>
       </c>
       <c r="D37" t="n">
-        <v>70</v>
+        <v>167</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>254.534641350211</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>4.285714285714286</v>
+        <v>0.5988023952095809</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I37" s="7" t="n">
-        <v>-18246.5325</v>
-      </c>
-      <c r="J37" s="6" t="n">
-        <v>0.5967040703552491</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>-40.32959296447509</v>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>15081.1775</v>
+        <v>8999</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>8999</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt;</t>
+          <t>{{campaign.name}} &gt; {{adset.name}} &gt; {{ad.name}}</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -29335,89 +29725,42 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>42507.28510548524</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>167</v>
+        <v>45</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>254.534641350211</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>0.5988023952095809</v>
+        <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I38" s="7" t="n">
-        <v>-6082.1775</v>
-      </c>
-      <c r="J38" s="6" t="n">
-        <v>0.5967040703552491</v>
-      </c>
-      <c r="K38" s="4" t="n">
-        <v>-40.32959296447508</v>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>15081.1775</v>
+        <v>0</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M38" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>{{campaign.name}} &gt; {{adset.name}} &gt; {{ad.name}}</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>45</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -29434,14 +29777,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Raw Meta Spend</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>456047.55</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Attributed Spend</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>282120.59</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Unallocated Spend</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>173926.96</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29454,14 +29837,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Funnel Stage</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Total Leads</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3534</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Paid Leads</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3465</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Unpaid Leads</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>69</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29643,9 +30066,9 @@
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
@@ -29741,17 +30164,17 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>webinar_type</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>registration_date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>registration_fee</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>webinar_type</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>registration_date</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -29833,10 +30256,10 @@
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" s="2" t="n">
-        <v/>
-      </c>
-      <c r="T2" s="3" t="n"/>
+      <c r="S2" s="3" t="n"/>
+      <c r="T2" s="2" t="n">
+        <v/>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>New</t>
@@ -29912,10 +30335,10 @@
       <c r="Q3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R3" s="2" t="n">
-        <v/>
-      </c>
-      <c r="T3" s="3" t="n"/>
+      <c r="S3" s="3" t="n"/>
+      <c r="T3" s="2" t="n">
+        <v/>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>New</t>
@@ -29991,16 +30414,16 @@
       <c r="Q4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="T4" s="3" t="n">
+      <c r="S4" s="3" t="n">
         <v>46245.96875</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>

--- a/output/report.xlsx
+++ b/output/report.xlsx
@@ -884,8 +884,8 @@
     <col width="9" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="19" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
@@ -986,12 +986,12 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>registration_fee</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>registration_date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>registration_fee</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -13063,7 +13063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -13140,25 +13140,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>C:49.0, AS:49.0, AD:49.0</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Mismatch</t>
-        </is>
+      <c r="E3" t="n">
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Campaign/AdSet/Ad Sales totals must equal Total Sales</t>
+          <t>Campaign/AdSet/Ad Sales totals must equal Attributed Sales (49). 3 unattributed sale(s) correctly excluded from summaries.</t>
         </is>
       </c>
     </row>
@@ -13170,25 +13168,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>467948</v>
+        <v>440951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>C:440951.0, AS:440951.0, AD:440951.0</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Mismatch</t>
-        </is>
+      <c r="E4" t="n">
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Campaign/AdSet/Ad Revenue totals must equal Total Revenue</t>
+          <t>Campaign/AdSet/Ad Revenue totals must equal Attributed Revenue (unattributed revenue excluded)</t>
         </is>
       </c>
     </row>
@@ -13283,24 +13279,18 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>&lt;10%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>5.8% (3)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Warn if &gt; 10%</t>
+          <t>Warn if &gt; 10% unattributed. Current: 5.8% (3 sales)</t>
         </is>
       </c>
     </row>
@@ -13463,7 +13453,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. Total Sales</t>
+          <t>INV. Revenue Formula</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -13472,24 +13462,24 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Golden Report verification for Total Sales</t>
+          <t>Attributed + Unattributed = Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. Attributed Sales</t>
+          <t>INV. Spend Formula</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -13498,24 +13488,24 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Golden Report verification for Attributed Sales</t>
+          <t>Attributed + Unallocated = Raw Meta Spend</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. Unattributed Sales</t>
+          <t>INV. Profit Formula</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -13524,353 +13514,15 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
-        <is>
-          <t>Golden Report verification for Unattributed Sales</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>G. Total Revenue</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>467948</v>
-      </c>
-      <c r="D18" t="n">
-        <v>467948</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Golden Report verification for Total Revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>G. Attributed Revenue</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>440951</v>
-      </c>
-      <c r="D19" t="n">
-        <v>440951</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Golden Report verification for Attributed Revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>G. Unattributed Revenue</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>26997</v>
-      </c>
-      <c r="D20" t="n">
-        <v>26997</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Golden Report verification for Unattributed Revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>G. Raw Meta Spend</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>456047.55</v>
-      </c>
-      <c r="D21" t="n">
-        <v>456047.55</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Golden Report verification for Raw Meta Spend</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>G. Attributed Spend</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>282120.59</v>
-      </c>
-      <c r="D22" t="n">
-        <v>282120.59</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Golden Report verification for Attributed Spend</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>G. Unallocated Spend</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>173926.96</v>
-      </c>
-      <c r="D23" t="n">
-        <v>173926.96</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Golden Report verification for Unallocated Spend</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>G. Profit</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>158830.41</v>
-      </c>
-      <c r="D24" t="n">
-        <v>158830.41</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Golden Report verification for Profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>G. ROAS</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Golden Report verification for ROAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>G. ROI %</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="D26" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Golden Report verification for ROI %</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>G. CAC</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>5757.56</v>
-      </c>
-      <c r="D27" t="n">
-        <v>5757.56</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Golden Report verification for CAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>INV. Revenue Formula</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Attributed + Unattributed = Total Revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>INV. Spend Formula</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Attributed + Unallocated = Raw Spend</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>INV. Profit Formula</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="inlineStr">
         <is>
           <t>Attributed Revenue - Attributed Spend = Profit</t>
         </is>
@@ -13928,8 +13580,8 @@
     <col width="50" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
@@ -14030,12 +13682,12 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>registration_fee</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>registration_date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>registration_fee</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -14149,11 +13801,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S2" s="3" t="n">
+      <c r="S2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="3" t="n">
         <v>46248.79236111111</v>
-      </c>
-      <c r="T2" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -14262,11 +13914,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S3" s="3" t="n">
+      <c r="S3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="3" t="n">
         <v>46243.98194444444</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -14375,11 +14027,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S4" s="3" t="n">
+      <c r="S4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="3" t="n">
         <v>46245.31944444445</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -14456,10 +14108,10 @@
       <c r="Q5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="3" t="n"/>
-      <c r="T5" s="2" t="n">
-        <v/>
-      </c>
+      <c r="S5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="T5" s="3" t="n"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>New</t>
@@ -14567,11 +14219,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S6" s="3" t="n">
+      <c r="S6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3" t="n">
         <v>46243.91458333333</v>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -14680,11 +14332,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S7" s="3" t="n">
+      <c r="S7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3" t="n">
         <v>46247.64097222222</v>
-      </c>
-      <c r="T7" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -14793,11 +14445,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S8" s="3" t="n">
+      <c r="S8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3" t="n">
         <v>46245.94930555556</v>
-      </c>
-      <c r="T8" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -14901,10 +14553,10 @@
       <c r="Q9" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="S9" s="3" t="n"/>
-      <c r="T9" s="2" t="n">
-        <v/>
-      </c>
+      <c r="S9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="T9" s="3" t="n"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>New</t>
@@ -15012,11 +14664,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S10" s="3" t="n">
+      <c r="S10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3" t="n">
         <v>46248.52986111111</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -15125,11 +14777,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S11" s="3" t="n">
+      <c r="S11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="3" t="n">
         <v>46249.45555555556</v>
-      </c>
-      <c r="T11" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -15233,10 +14885,10 @@
       <c r="Q12" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="S12" s="3" t="n"/>
-      <c r="T12" s="2" t="n">
-        <v/>
-      </c>
+      <c r="S12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="T12" s="3" t="n"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>New</t>
@@ -15344,11 +14996,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S13" s="3" t="n">
+      <c r="S13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3" t="n">
         <v>46244.9875</v>
-      </c>
-      <c r="T13" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -15457,11 +15109,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S14" s="3" t="n">
+      <c r="S14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="n">
         <v>46248.38263888889</v>
-      </c>
-      <c r="T14" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -15570,11 +15222,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S15" s="3" t="n">
+      <c r="S15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3" t="n">
         <v>46247.81805555556</v>
-      </c>
-      <c r="T15" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -15683,11 +15335,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S16" s="3" t="n">
+      <c r="S16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="3" t="n">
         <v>46247.56875</v>
-      </c>
-      <c r="T16" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -15791,10 +15443,10 @@
       <c r="Q17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S17" s="3" t="n"/>
-      <c r="T17" s="2" t="n">
-        <v/>
-      </c>
+      <c r="S17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="T17" s="3" t="n"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>New</t>
@@ -15902,11 +15554,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S18" s="3" t="n">
+      <c r="S18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3" t="n">
         <v>46248.38333333333</v>
-      </c>
-      <c r="T18" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -15983,10 +15635,10 @@
       <c r="Q19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S19" s="3" t="n"/>
-      <c r="T19" s="2" t="n">
-        <v/>
-      </c>
+      <c r="S19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="T19" s="3" t="n"/>
       <c r="U19" t="inlineStr">
         <is>
           <t>New</t>
@@ -16094,11 +15746,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S20" s="3" t="n">
+      <c r="S20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3" t="n">
         <v>46244.35347222222</v>
-      </c>
-      <c r="T20" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -16207,11 +15859,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S21" s="3" t="n">
+      <c r="S21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3" t="n">
         <v>46243.49444444444</v>
-      </c>
-      <c r="T21" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -16320,11 +15972,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S22" s="3" t="n">
+      <c r="S22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3" t="n">
         <v>46245.81666666667</v>
-      </c>
-      <c r="T22" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -16428,10 +16080,10 @@
       <c r="Q23" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="S23" s="3" t="n"/>
-      <c r="T23" s="2" t="n">
-        <v/>
-      </c>
+      <c r="S23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="T23" s="3" t="n"/>
       <c r="U23" t="inlineStr">
         <is>
           <t>New</t>
@@ -16539,11 +16191,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S24" s="3" t="n">
+      <c r="S24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3" t="n">
         <v>46247.375</v>
-      </c>
-      <c r="T24" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -16652,11 +16304,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S25" s="3" t="n">
+      <c r="S25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3" t="n">
         <v>46245.99861111111</v>
-      </c>
-      <c r="T25" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -16765,11 +16417,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S26" s="3" t="n">
+      <c r="S26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3" t="n">
         <v>46247.32152777778</v>
-      </c>
-      <c r="T26" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -16873,10 +16525,10 @@
       <c r="Q27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S27" s="3" t="n"/>
-      <c r="T27" s="2" t="n">
-        <v/>
-      </c>
+      <c r="S27" s="2" t="n">
+        <v/>
+      </c>
+      <c r="T27" s="3" t="n"/>
       <c r="U27" t="inlineStr">
         <is>
           <t>New</t>
@@ -16957,11 +16609,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S28" s="3" t="n">
+      <c r="S28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3" t="n">
         <v>46245.96875</v>
-      </c>
-      <c r="T28" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -17070,11 +16722,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S29" s="3" t="n">
+      <c r="S29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3" t="n">
         <v>46244.92986111111</v>
-      </c>
-      <c r="T29" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -17183,11 +16835,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S30" s="3" t="n">
+      <c r="S30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3" t="n">
         <v>46247.72847222222</v>
-      </c>
-      <c r="T30" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -17291,10 +16943,10 @@
       <c r="Q31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S31" s="3" t="n"/>
-      <c r="T31" s="2" t="n">
-        <v/>
-      </c>
+      <c r="S31" s="2" t="n">
+        <v/>
+      </c>
+      <c r="T31" s="3" t="n"/>
       <c r="U31" t="inlineStr">
         <is>
           <t>New</t>
@@ -17402,11 +17054,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S32" s="3" t="n">
+      <c r="S32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3" t="n">
         <v>46243.63055555556</v>
-      </c>
-      <c r="T32" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -17515,11 +17167,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S33" s="3" t="n">
+      <c r="S33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3" t="n">
         <v>46246.63958333333</v>
-      </c>
-      <c r="T33" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -17623,10 +17275,10 @@
       <c r="Q34" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="S34" s="3" t="n"/>
-      <c r="T34" s="2" t="n">
-        <v/>
-      </c>
+      <c r="S34" s="2" t="n">
+        <v/>
+      </c>
+      <c r="T34" s="3" t="n"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>New</t>
@@ -17734,11 +17386,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S35" s="3" t="n">
+      <c r="S35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3" t="n">
         <v>46248.97569444445</v>
-      </c>
-      <c r="T35" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -17847,11 +17499,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S36" s="3" t="n">
+      <c r="S36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="3" t="n">
         <v>46247.53958333333</v>
-      </c>
-      <c r="T36" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -17960,11 +17612,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S37" s="3" t="n">
+      <c r="S37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="3" t="n">
         <v>46245.68472222222</v>
-      </c>
-      <c r="T37" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -18073,11 +17725,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S38" s="3" t="n">
+      <c r="S38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="3" t="n">
         <v>46247.77708333333</v>
-      </c>
-      <c r="T38" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -18181,10 +17833,10 @@
       <c r="Q39" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="S39" s="3" t="n"/>
-      <c r="T39" s="2" t="n">
-        <v/>
-      </c>
+      <c r="S39" s="2" t="n">
+        <v/>
+      </c>
+      <c r="T39" s="3" t="n"/>
       <c r="U39" t="inlineStr">
         <is>
           <t>New</t>
@@ -18292,11 +17944,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S40" s="3" t="n">
+      <c r="S40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="3" t="n">
         <v>46245.82361111111</v>
-      </c>
-      <c r="T40" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -18405,11 +18057,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S41" s="3" t="n">
+      <c r="S41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="3" t="n">
         <v>46245.41875</v>
-      </c>
-      <c r="T41" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -18513,10 +18165,10 @@
       <c r="Q42" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="S42" s="3" t="n"/>
-      <c r="T42" s="2" t="n">
-        <v/>
-      </c>
+      <c r="S42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="T42" s="3" t="n"/>
       <c r="U42" t="inlineStr">
         <is>
           <t>New</t>
@@ -18619,10 +18271,10 @@
       <c r="Q43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S43" s="3" t="n"/>
-      <c r="T43" s="2" t="n">
-        <v/>
-      </c>
+      <c r="S43" s="2" t="n">
+        <v/>
+      </c>
+      <c r="T43" s="3" t="n"/>
       <c r="U43" t="inlineStr">
         <is>
           <t>New</t>
@@ -18730,11 +18382,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S44" s="3" t="n">
+      <c r="S44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3" t="n">
         <v>46244.30694444444</v>
-      </c>
-      <c r="T44" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -18843,11 +18495,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S45" s="3" t="n">
+      <c r="S45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3" t="n">
         <v>46248.91944444444</v>
-      </c>
-      <c r="T45" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -18956,11 +18608,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S46" s="3" t="n">
+      <c r="S46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="3" t="n">
         <v>46243.27708333333</v>
-      </c>
-      <c r="T46" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -19064,10 +18716,10 @@
       <c r="Q47" s="2" t="n">
         <v>10080.81</v>
       </c>
-      <c r="S47" s="3" t="n"/>
-      <c r="T47" s="2" t="n">
-        <v/>
-      </c>
+      <c r="S47" s="2" t="n">
+        <v/>
+      </c>
+      <c r="T47" s="3" t="n"/>
       <c r="U47" t="inlineStr">
         <is>
           <t>New</t>
@@ -19175,11 +18827,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S48" s="3" t="n">
+      <c r="S48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3" t="n">
         <v>46246.52708333333</v>
-      </c>
-      <c r="T48" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -19288,11 +18940,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S49" s="3" t="n">
+      <c r="S49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3" t="n">
         <v>46243.63333333333</v>
-      </c>
-      <c r="T49" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -19401,11 +19053,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S50" s="3" t="n">
+      <c r="S50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3" t="n">
         <v>46249.40625</v>
-      </c>
-      <c r="T50" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -19514,11 +19166,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S51" s="3" t="n">
+      <c r="S51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3" t="n">
         <v>46248.67083333333</v>
-      </c>
-      <c r="T51" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -19623,10 +19275,10 @@
       <c r="Q52" s="2" t="n">
         <v>10080.81</v>
       </c>
-      <c r="S52" s="3" t="n"/>
-      <c r="T52" s="2" t="n">
-        <v/>
-      </c>
+      <c r="S52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="T52" s="3" t="n"/>
       <c r="U52" t="inlineStr">
         <is>
           <t>New</t>
@@ -19729,10 +19381,10 @@
       <c r="Q53" s="2" t="n">
         <v>8275.590714285714</v>
       </c>
-      <c r="S53" s="3" t="n"/>
-      <c r="T53" s="2" t="n">
-        <v/>
-      </c>
+      <c r="S53" s="2" t="n">
+        <v/>
+      </c>
+      <c r="T53" s="3" t="n"/>
       <c r="U53" t="inlineStr">
         <is>
           <t>New</t>
@@ -30067,8 +29719,8 @@
     <col width="9" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
@@ -30169,12 +29821,12 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>registration_fee</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>registration_date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>registration_fee</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -30256,10 +29908,10 @@
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" s="3" t="n"/>
-      <c r="T2" s="2" t="n">
-        <v/>
-      </c>
+      <c r="S2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="T2" s="3" t="n"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>New</t>
@@ -30335,10 +29987,10 @@
       <c r="Q3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="3" t="n"/>
-      <c r="T3" s="2" t="n">
-        <v/>
-      </c>
+      <c r="S3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="T3" s="3" t="n"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>New</t>
@@ -30419,11 +30071,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="S4" s="3" t="n">
+      <c r="S4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="3" t="n">
         <v>46245.96875</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
